--- a/tables/Table S7.xlsx
+++ b/tables/Table S7.xlsx
@@ -2,22 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17900" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,17 +26,49 @@
     </font>
     <font>
       <name val="Times New Roman"/>
+      <family val="1"/>
       <b val="1"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Times New Roman"/>
+      <family val="1"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Times New Roman"/>
+      <family val="1"/>
       <i val="1"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <b val="1"/>
+      <i val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <i val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <b val="1"/>
+      <sz val="9"/>
+      <vertAlign val="subscript"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <b val="1"/>
+      <sz val="9"/>
+      <vertAlign val="superscript"/>
     </font>
   </fonts>
   <fills count="2">
@@ -48,7 +79,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -57,53 +88,90 @@
       <diagonal/>
     </border>
     <border>
-      <bottom style="medium"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium"/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
+      <left/>
       <right/>
-      <bottom style="medium"/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -467,30 +535,21 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="5" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="8.1640625" customWidth="1" min="1" max="1"/>
+    <col width="10.33203125" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="2.33203125" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="5.83203125" bestFit="1" customWidth="1" min="4" max="13"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+    <row r="1" ht="16" customHeight="1" thickBot="1">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Species</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>pH</t>
         </is>
@@ -500,21 +559,71 @@
           <t>n</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Day (net change, µmol L-1)</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>Night (net change, µmol L-1)</t>
-        </is>
-      </c>
+      <c r="D1" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t>Day (net change, µmol L</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+              <b val="1"/>
+              <sz val="9"/>
+              <vertAlign val="superscript"/>
+            </rPr>
+            <t>-1</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t>)</t>
+          </r>
+        </is>
+      </c>
+      <c r="E1" s="11" t="n"/>
+      <c r="F1" s="11" t="n"/>
+      <c r="G1" s="11" t="n"/>
+      <c r="H1" s="11" t="n"/>
+      <c r="I1" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t>Night (net change, µmol L</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+              <b val="1"/>
+              <sz val="9"/>
+              <vertAlign val="superscript"/>
+            </rPr>
+            <t>-1</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t>)</t>
+          </r>
+        </is>
+      </c>
+      <c r="J1" s="11" t="n"/>
+      <c r="K1" s="11" t="n"/>
+      <c r="L1" s="11" t="n"/>
+      <c r="M1" s="11" t="n"/>
     </row>
-    <row r="2">
-      <c r="A2" s="7" t="n"/>
-      <c r="B2" s="7" t="n"/>
-      <c r="C2" s="7" t="n"/>
+    <row r="2" ht="16" customHeight="1" thickBot="1">
+      <c r="A2" s="14" t="n"/>
+      <c r="B2" s="14" t="n"/>
+      <c r="C2" s="14" t="n"/>
       <c r="D2" s="1" t="inlineStr">
         <is>
           <t>Si</t>
@@ -522,22 +631,110 @@
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>NO2-</t>
+          <r>
+            <t>NO</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+              <b val="1"/>
+              <sz val="9"/>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>2</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+              <b val="1"/>
+              <sz val="9"/>
+              <vertAlign val="superscript"/>
+            </rPr>
+            <t>-</t>
+          </r>
         </is>
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
-          <t>NO3-</t>
+          <r>
+            <t>NO</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+              <b val="1"/>
+              <sz val="9"/>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>3</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+              <b val="1"/>
+              <sz val="9"/>
+              <vertAlign val="superscript"/>
+            </rPr>
+            <t>-</t>
+          </r>
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
-          <t>NH4+</t>
+          <r>
+            <t>NH</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+              <b val="1"/>
+              <sz val="9"/>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>4</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+              <b val="1"/>
+              <sz val="9"/>
+              <vertAlign val="superscript"/>
+            </rPr>
+            <t>+</t>
+          </r>
         </is>
       </c>
       <c r="H2" s="1" t="inlineStr">
         <is>
-          <t>PO43-</t>
+          <r>
+            <t>PO</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+              <b val="1"/>
+              <sz val="9"/>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>4</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+              <b val="1"/>
+              <sz val="9"/>
+              <vertAlign val="superscript"/>
+            </rPr>
+            <t>3-</t>
+          </r>
         </is>
       </c>
       <c r="I2" s="1" t="inlineStr">
@@ -547,273 +744,401 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>NO2-</t>
+          <r>
+            <t>NO</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+              <b val="1"/>
+              <sz val="9"/>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>2</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+              <b val="1"/>
+              <sz val="9"/>
+              <vertAlign val="superscript"/>
+            </rPr>
+            <t>-</t>
+          </r>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>NO3-</t>
+          <r>
+            <t>NO</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+              <b val="1"/>
+              <sz val="9"/>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>3</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+              <b val="1"/>
+              <sz val="9"/>
+              <vertAlign val="superscript"/>
+            </rPr>
+            <t>-</t>
+          </r>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t>NH4+</t>
+          <r>
+            <t>NH</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+              <b val="1"/>
+              <sz val="9"/>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>4</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+              <b val="1"/>
+              <sz val="9"/>
+              <vertAlign val="superscript"/>
+            </rPr>
+            <t>+</t>
+          </r>
         </is>
       </c>
       <c r="M2" s="1" t="inlineStr">
         <is>
-          <t>PO43-</t>
+          <r>
+            <t>PO</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+              <b val="1"/>
+              <sz val="9"/>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>4</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+              <b val="1"/>
+              <sz val="9"/>
+              <vertAlign val="superscript"/>
+            </rPr>
+            <t>3-</t>
+          </r>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Orbicella faveolata</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C3" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>0.026 (0.065)</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>0.015 (0.034)</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>-0.332 (0.039)</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>-0.909 (0.170)</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>-0.016 (0.079)</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>-0.026 (0.055)</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>0.007 (0.003)</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>-0.392 (0.102)</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>-0.285 (0.207)</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>-0.046 (0.014)</t>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>0.026
+(0.065)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>0.015
+(0.034)</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>-0.332
+(0.039)</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>-0.909
+(0.170)</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>-0.016
+(0.079)</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>-0.026
+(0.055)</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>0.007
+(0.003)</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>-0.392
+(0.102)</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>-0.285
+(0.207)</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>-0.046
+(0.014)</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" s="4" t="inlineStr">
+    <row r="4" ht="26" customHeight="1">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Acidified</t>
         </is>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>-0.441 (0.066)</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>0.009 (0.010)</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>-0.318 (0.051)</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>-0.025 (0.035)</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>0.190 (0.103)</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>-0.387 (0.128)</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>-0.005 (0.005)</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>-0.068 (0.209)</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>-0.363 (0.127)</t>
-        </is>
-      </c>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>0.097 (0.038)</t>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-0.441
+(0.066)</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0.009
+(0.010)</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>-0.318
+(0.051)</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>-0.025
+(0.035)</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0.190
+(0.103)</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>-0.387
+(0.128)</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>-0.005
+(0.005)</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>-0.068
+(0.209)</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>-0.363
+(0.127)</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>0.097
+(0.038)</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Siderastrea siderea</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>-0.389 (0.198)</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>-0.006 (0.004)</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>-0.480 (0.148)</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>-1.421 (0.407)</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>-0.067 (0.009)</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>-0.787 (0.206)</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>-0.021 (0.009)</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>-0.322 (0.036)</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>-0.350 (0.213)</t>
-        </is>
-      </c>
-      <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t>-0.099 (0.008)</t>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>-0.389
+(0.198)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>-0.006
+(0.004)</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>-0.480
+(0.148)</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>-1.421
+(0.407)</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>-0.067
+(0.009)</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>-0.787
+(0.206)</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>-0.021
+(0.009)</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>-0.322
+(0.036)</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>-0.350
+(0.213)</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>-0.099
+(0.008)</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="7" t="n"/>
-      <c r="B6" s="6" t="inlineStr">
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="14" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Acidified</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>-0.503 (0.124)</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>-0.018 (0.002)</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>-0.652 (0.079)</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>-0.896 (0.100)</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>-0.026 (0.010)</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>-0.352 (0.194)</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>0.001 (0.010)</t>
-        </is>
-      </c>
-      <c r="K6" s="6" t="inlineStr">
-        <is>
-          <t>-0.168 (0.087)</t>
-        </is>
-      </c>
-      <c r="L6" s="6" t="inlineStr">
-        <is>
-          <t>0.069 (0.453)</t>
-        </is>
-      </c>
-      <c r="M6" s="6" t="inlineStr">
-        <is>
-          <t>-0.031 (0.035)</t>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>-0.503
+(0.124)</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>-0.018
+(0.002)</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>-0.652
+(0.079)</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>-0.896
+(0.100)</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>-0.026
+(0.010)</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>-0.352
+(0.194)</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>0.001
+(0.010)</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>-0.168
+(0.087)</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>0.069
+(0.453)</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-0.031
+(0.035)</t>
         </is>
       </c>
     </row>
